--- a/models/sovereigns/Kuwait_Sovereign_Model.xlsx
+++ b/models/sovereigns/Kuwait_Sovereign_Model.xlsx
@@ -637,16 +637,34 @@
           <t>policy_rate_pct</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
+      <c r="B3" s="2" t="n">
+        <v>3.5</v>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BIS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>09-Oct-26</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BIS WS_CBPOL monthly series (auto-filled; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -671,16 +689,34 @@
           <t>cpi_latest_yoy_pct</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IMF CPI database</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>09-Oct-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IMF CPI database, all items, y/y % change, monthly (auto-filled; a run's sourced point replaces it unless older)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -949,7 +985,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>51.738</v>
+        <v>32.689</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -958,12 +994,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>World Bank WDI</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -973,7 +1009,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Kuwait_Sovereign_Model.xlsx
+++ b/models/sovereigns/Kuwait_Sovereign_Model.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>Sep-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -660,11 +660,7 @@
           <t>09-Oct-26</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>BIS WS_CBPOL monthly series (auto-filled; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -777,7 +773,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>22.3</v>
+        <v>2.9</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -786,12 +782,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>FY24/25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>Search summary of debt law coverage (tier 4)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -801,7 +797,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
+          <t>Gross government debt, press forecast path (about 12% by FY27/28); conflicts with repo WEO 22.3%, unresolved</t>
         </is>
       </c>
     </row>
@@ -829,7 +825,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>27.6</v>
+        <v>-18.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -838,24 +834,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>FY26/27 draft budget (KD 9.8bn / $31.9bn deficit over repo nominal GDP, derived)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>Arab News, Kuwait Times, TradeArabia; ratio derived in the adjudicated document</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+          <t>28-Feb-26</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -915,7 +907,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>26</v>
+        <v>18.8</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -924,12 +916,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>2025-Q2 to 2026-Q1 (4-quarter sum USD 32.54bn over repo nominal GDP, derived)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>IMF BOP via repo data record; ratio derived in the adjudicated document</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -937,11 +929,7 @@
           <t>09-Oct-26</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -994,7 +982,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>Aug-26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1009,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gross official reserves incl. gold at national valuation, end-month (auto-filled; a run's sourced point replaces it unless older)</t>
+          <t>CBK gross reserves incl. gold (gold USD 0.103bn)</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1025,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>8.406000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1059,11 +1047,7 @@
           <t>09-Oct-26</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1123,7 +1107,7 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>172.92</v>
+        <v>172.9</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1132,12 +1116,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026E</t>
+          <t>not stated in repo record</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IMF WEO</t>
+          <t>Repo data record database/sovereigns/kuwait.json (IMF WEO via repo)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1145,11 +1129,7 @@
           <t>09-Oct-26</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>official annual series (filled automatically; a run's sourced point replaces it)</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1247,6 +1227,21 @@
           <t>fitch</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Aug-26</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1254,11 +1249,31 @@
           <t>sp</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21-Nov-25</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>moodys</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Stable</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Kuwait_Sovereign_Model.xlsx
+++ b/models/sovereigns/Kuwait_Sovereign_Model.xlsx
@@ -787,17 +787,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Search summary of debt law coverage (tier 4)</t>
+          <t>Search summary on debt law (tier 4)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gross government debt, press forecast path (about 12% by FY27/28); conflicts with repo WEO 22.3%, unresolved</t>
+          <t>Gross government debt, FY24/25 (press/search summary); repo WEO 2026E shows 22.3% and is unreconciled</t>
         </is>
       </c>
     </row>
@@ -834,17 +834,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY26/27 draft budget (KD 9.8bn / $31.9bn deficit over repo nominal GDP, derived)</t>
+          <t>FY26/27 draft budget (KD 9.8bn / $31.9bn deficit over repo nominal GDP; derived)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arab News, Kuwait Times, TradeArabia; ratio derived in the adjudicated document</t>
+          <t>Arab News, Kuwait Times, TradeArabia; repo nominal GDP; derived</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28-Feb-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -916,12 +916,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-Q2 to 2026-Q1 (4-quarter sum USD 32.54bn over repo nominal GDP, derived)</t>
+          <t>2025-Q2 to 2026-Q1 (sum of four quarters, USD 32.5bn over repo nominal GDP; derived)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF BOP via repo data record; ratio derived in the adjudicated document</t>
+          <t>IMF BOP via repo data record; derived</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1114,14 +1114,10 @@
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>not stated in repo record</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Repo data record database/sovereigns/kuwait.json (IMF WEO via repo)</t>
+          <t>Repo data record, database/sovereigns/kuwait.json (IMF WEO)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">

--- a/models/sovereigns/Kuwait_Sovereign_Model.xlsx
+++ b/models/sovereigns/Kuwait_Sovereign_Model.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BIS</t>
+          <t>BIS (CBK policy rate, unchanged Apr-Sep-26)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Search summary on debt law (tier 4)</t>
+          <t>Search summary on public debt law (tier 4)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gross government debt, FY24/25 (press/search summary); repo WEO 2026E shows 22.3% and is unreconciled</t>
+          <t>Gross government debt forecast from search summary; conflicts with repo WEO 2026E 22.3% (unresolved, open item 2)</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY26/27 draft budget (KD 9.8bn / $31.9bn deficit over repo nominal GDP; derived)</t>
+          <t>FY26/27 draft budget (KD 9.8bn / USD 31.9bn deficit over repo nominal GDP; derived)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>28-Feb-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-Q2 to 2026-Q1 (sum of four quarters, USD 32.5bn over repo nominal GDP; derived)</t>
+          <t>2025-Q2 to 2026-Q1 (sum of 4 quarters, USD 32.5bn, over repo nominal GDP; derived)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBK gross reserves incl. gold (gold USD 0.103bn)</t>
+          <t>CBK gross reserves incl. gold (gold USD 0.103bn); central bank liquid pool, excludes KIA/FGF assets</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Repo data record, database/sovereigns/kuwait.json (IMF WEO)</t>
+          <t>IMF WEO via repo data record (vintage unverified)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1305,6 +1305,11 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1315,7 +1320,8 @@
           <t>nominal_gdp_usd_bn</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1323,7 +1329,8 @@
           <t>real_gdp_growth_pct</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1331,7 +1338,8 @@
           <t>cpi_avg_pct</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1339,7 +1347,8 @@
           <t>current_account_pct_gdp</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1347,7 +1356,8 @@
           <t>fiscal_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1355,7 +1365,8 @@
           <t>primary_balance_pct_gdp</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1363,7 +1374,8 @@
           <t>gov_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1371,7 +1383,8 @@
           <t>external_debt_pct_gdp</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1379,7 +1392,14 @@
           <t>gross_reserves_usd_bn</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" s="2" t="n">
+        <v>32.689</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IMF International Liquidity, Aug-26 observation (gross incl. gold), 09-Oct-26</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1387,7 +1407,8 @@
           <t>revenue_pct_gdp</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1395,7 +1416,8 @@
           <t>interest_pct_revenue</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Kuwait_Sovereign_Model.xlsx
+++ b/models/sovereigns/Kuwait_Sovereign_Model.xlsx
@@ -787,17 +787,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Search summary on public debt law (tier 4)</t>
+          <t>Search summary on public debt law</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>Oct-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gross government debt forecast from search summary; conflicts with repo WEO 2026E 22.3% (unresolved, open item 2)</t>
+          <t>gross government debt, FY24/25; search summary (tier 4, Low confidence); conflicts with repo WEO 2026E 22.3% which is unverified</t>
         </is>
       </c>
     </row>
@@ -834,17 +834,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FY26/27 draft budget (KD 9.8bn / USD 31.9bn deficit over repo nominal GDP; derived)</t>
+          <t>FY26/27 draft budget (KD 9.8bn / $31.9bn deficit over repo nominal GDP USD 172.9bn; derived)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arab News, Kuwait Times, TradeArabia; repo nominal GDP; derived</t>
+          <t>Arab News, Kuwait Times, TradeArabia (Feb-26); derived against IMF WEO nominal GDP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28-Feb-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -916,12 +916,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-Q2 to 2026-Q1 (sum of 4 quarters, USD 32.5bn, over repo nominal GDP; derived)</t>
+          <t>2025-Q2 to 2026-Q1 (four-quarter sum USD 32.5bn over repo nominal GDP; derived)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMF BOP via repo data record; derived</t>
+          <t>IMF BOP via repo data record; derived against IMF WEO nominal GDP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMF International Liquidity</t>
+          <t>IMF International Liquidity via repo data record</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CBK gross reserves incl. gold (gold USD 0.103bn); central bank liquid pool, excludes KIA/FGF assets</t>
+          <t>gross incl. gold (gold USD 0.103bn); CBK liquid pool, excludes KIA/FGF assets</t>
         </is>
       </c>
     </row>
@@ -1114,10 +1114,14 @@
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>IMF WEO vintage and year unverified</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record (vintage unverified)</t>
+          <t>IMF WEO via repo data record database/sovereigns/kuwait.json</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">

--- a/models/sovereigns/Kuwait_Sovereign_Model.xlsx
+++ b/models/sovereigns/Kuwait_Sovereign_Model.xlsx
@@ -652,12 +652,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BIS (CBK policy rate, unchanged Apr-Sep-26)</t>
+          <t>BIS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>30-Sep-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -792,12 +792,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oct-26</t>
+          <t>09-Oct-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>gross government debt, FY24/25; search summary (tier 4, Low confidence); conflicts with repo WEO 2026E 22.3% which is unverified</t>
+          <t>gross debt, press/search summary; conflicts with repo WEO 22.3% for 2026E (vintage and basis unresolved)</t>
         </is>
       </c>
     </row>
@@ -987,7 +987,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IMF International Liquidity via repo data record</t>
+          <t>IMF International Liquidity</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>gross incl. gold (gold USD 0.103bn); CBK liquid pool, excludes KIA/FGF assets</t>
+          <t>CBK gross reserves incl. gold (gold USD 0.103bn)</t>
         </is>
       </c>
     </row>
@@ -1114,14 +1114,10 @@
           <t>USD bn</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>IMF WEO vintage and year unverified</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IMF WEO via repo data record database/sovereigns/kuwait.json</t>
+          <t>Repo data record database/sovereigns/kuwait.json (IMF WEO)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1295,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1314,6 +1310,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FY24/25</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
@@ -1325,7 +1326,8 @@
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1334,7 +1336,8 @@
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1343,7 +1346,8 @@
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1352,7 +1356,8 @@
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1361,7 +1366,8 @@
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1370,7 +1376,8 @@
         </is>
       </c>
       <c r="B7" s="2" t="n"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1379,7 +1386,14 @@
         </is>
       </c>
       <c r="B8" s="2" t="n"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Search summary on public debt law, 09-Oct-26 (unverified; conflicts with repo WEO)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1388,7 +1402,8 @@
         </is>
       </c>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1399,7 +1414,8 @@
       <c r="B10" s="2" t="n">
         <v>32.689</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>IMF International Liquidity, Aug-26 observation (gross incl. gold), 09-Oct-26</t>
         </is>
@@ -1412,7 +1428,8 @@
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1421,7 +1438,8 @@
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/models/sovereigns/Kuwait_Sovereign_Model.xlsx
+++ b/models/sovereigns/Kuwait_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 09-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/kuwait.json</t>
+          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/kuwait.json</t>
         </is>
       </c>
     </row>

--- a/models/sovereigns/Kuwait_Sovereign_Model.xlsx
+++ b/models/sovereigns/Kuwait_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 12-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/kuwait.json</t>
+          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/kuwait.json</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sep-26</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -657,10 +657,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Sep-26</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>19-Oct-26</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>BIS WS_CBPOL monthly series (auto-filled; a run's sourced point replaces it)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>09-Oct-26</t>
+          <t>19-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/models/sovereigns/Kuwait_Sovereign_Model.xlsx
+++ b/models/sovereigns/Kuwait_Sovereign_Model.xlsx
@@ -590,7 +590,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>built 19-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/kuwait.json</t>
+          <t>built 26-Oct-26 by pipeline/sovereign_model.py from database/sovereigns/kuwait.json</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19-Oct-26</t>
+          <t>26-Oct-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
